--- a/data/trans_orig/P27_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P27_2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2007</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2007 (tasa de respuesta: 94,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70088</t>
+          <t>70528</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105130</t>
+          <t>105606</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34784</t>
+          <t>34696</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60094</t>
+          <t>59741</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112445</t>
+          <t>111871</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156831</t>
+          <t>155571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274022</t>
+          <t>275438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>326072</t>
+          <t>323594</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231351</t>
+          <t>231340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>278935</t>
+          <t>280799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516844</t>
+          <t>522976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>584523</t>
+          <t>587603</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>133587</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>176243</t>
+          <t>177713</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>150936</t>
+          <t>148456</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>196011</t>
+          <t>193226</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>294067</t>
+          <t>297044</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>357018</t>
+          <t>358923</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101810</t>
+          <t>102560</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>142429</t>
+          <t>140787</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147780</t>
+          <t>147132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>189746</t>
+          <t>190414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260897</t>
+          <t>259679</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>320081</t>
+          <t>317719</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>115563</t>
+          <t>116044</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>162921</t>
+          <t>163024</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64713</t>
+          <t>64565</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>99268</t>
+          <t>98610</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>192429</t>
+          <t>192567</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>248373</t>
+          <t>248056</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>344417</t>
+          <t>344092</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>408076</t>
+          <t>405228</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>279991</t>
+          <t>278814</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>336842</t>
+          <t>336922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>634130</t>
+          <t>638280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>716760</t>
+          <t>722331</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>207450</t>
+          <t>209842</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262323</t>
+          <t>265925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251617</t>
+          <t>252493</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>306050</t>
+          <t>307640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>475445</t>
+          <t>473259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>556021</t>
+          <t>555253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>154548</t>
+          <t>149577</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>203601</t>
+          <t>198177</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>240376</t>
+          <t>241198</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>294156</t>
+          <t>297050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>406388</t>
+          <t>404362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>487910</t>
+          <t>478835</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49994</t>
+          <t>51132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82521</t>
+          <t>82784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35979</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61079</t>
+          <t>60501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92539</t>
+          <t>92547</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>133124</t>
+          <t>134622</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>237665</t>
+          <t>238782</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>291000</t>
+          <t>292869</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>161791</t>
+          <t>161493</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>206195</t>
+          <t>207591</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>414622</t>
+          <t>410923</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>483846</t>
+          <t>480706</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136637</t>
+          <t>139764</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>183767</t>
+          <t>183153</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>157004</t>
+          <t>159844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>203311</t>
+          <t>204187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>310269</t>
+          <t>309089</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>372804</t>
+          <t>374937</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140237</t>
+          <t>139426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188183</t>
+          <t>182922</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>228089</t>
+          <t>228382</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>275584</t>
+          <t>276868</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>381032</t>
+          <t>379407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>448796</t>
+          <t>446301</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119858</t>
+          <t>118088</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>160424</t>
+          <t>160107</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72663</t>
+          <t>73143</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109836</t>
+          <t>110855</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>203623</t>
+          <t>203836</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>261068</t>
+          <t>260589</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>308089</t>
+          <t>311481</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>363989</t>
+          <t>366903</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>305438</t>
+          <t>305849</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>365399</t>
+          <t>366767</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>630779</t>
+          <t>631891</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>713604</t>
+          <t>713459</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>218180</t>
+          <t>220344</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269872</t>
+          <t>273210</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>244132</t>
+          <t>245686</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>300780</t>
+          <t>303122</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>481698</t>
+          <t>481152</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>561514</t>
+          <t>557908</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138011</t>
+          <t>138266</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>181654</t>
+          <t>179355</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>242317</t>
+          <t>244853</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>302266</t>
+          <t>301721</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>390784</t>
+          <t>390910</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>464366</t>
+          <t>460771</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>389288</t>
+          <t>391302</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>466944</t>
+          <t>469969</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>234875</t>
+          <t>236178</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>299242</t>
+          <t>297364</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>648353</t>
+          <t>645550</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>750053</t>
+          <t>747682</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1219424</t>
+          <t>1220083</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1329864</t>
+          <t>1329544</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1022865</t>
+          <t>1024648</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1132879</t>
+          <t>1133255</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2282017</t>
+          <t>2275752</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2434584</t>
+          <t>2434026</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>747697</t>
+          <t>749669</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>848249</t>
+          <t>846049</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>852377</t>
+          <t>853016</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>957369</t>
+          <t>951071</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1630126</t>
+          <t>1635900</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1769085</t>
+          <t>1783378</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>568437</t>
+          <t>570250</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>659594</t>
+          <t>662103</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>906965</t>
+          <t>910868</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1010862</t>
+          <t>1010245</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1505976</t>
+          <t>1506877</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1641932</t>
+          <t>1640378</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2012</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2012 (tasa de respuesta: 96,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>11533</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30065</t>
+          <t>27752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20447</t>
+          <t>20035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41102</t>
+          <t>41192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39964</t>
+          <t>40618</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68473</t>
+          <t>68787</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20786</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42742</t>
+          <t>43602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65484</t>
+          <t>66815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102048</t>
+          <t>101700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68808</t>
+          <t>67672</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104756</t>
+          <t>102114</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58542</t>
+          <t>59348</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93549</t>
+          <t>93086</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>136672</t>
+          <t>136364</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>184590</t>
+          <t>185414</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>521241</t>
+          <t>522367</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>564562</t>
+          <t>565511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>546956</t>
+          <t>548457</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>589687</t>
+          <t>589600</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1084461</t>
+          <t>1080605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1144684</t>
+          <t>1144252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,55%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23659</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47888</t>
+          <t>47448</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34511</t>
+          <t>36857</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>44996</t>
+          <t>44354</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>75850</t>
+          <t>75034</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55717</t>
+          <t>57060</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90354</t>
+          <t>92044</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43425</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71753</t>
+          <t>72547</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107464</t>
+          <t>105910</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151474</t>
+          <t>153184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98535</t>
+          <t>99547</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>139638</t>
+          <t>140765</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73803</t>
+          <t>75149</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112776</t>
+          <t>112563</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182431</t>
+          <t>182756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237619</t>
+          <t>238728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>756803</t>
+          <t>754136</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>811959</t>
+          <t>806820</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>825792</t>
+          <t>823999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>873753</t>
+          <t>872047</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1597124</t>
+          <t>1593116</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1668779</t>
+          <t>1668057</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7555</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22554</t>
+          <t>24305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32688</t>
+          <t>33796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41090</t>
+          <t>40248</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>23672</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46464</t>
+          <t>46738</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>48356</t>
+          <t>46576</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>78815</t>
+          <t>78478</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62028</t>
+          <t>63347</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>95952</t>
+          <t>98481</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55559</t>
+          <t>56256</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88568</t>
+          <t>89560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126659</t>
+          <t>124516</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175853</t>
+          <t>172495</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>600789</t>
+          <t>598549</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>642337</t>
+          <t>641238</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>635010</t>
+          <t>636099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>676231</t>
+          <t>674669</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1246476</t>
+          <t>1250345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1305707</t>
+          <t>1307999</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,54%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36455</t>
+          <t>37308</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15983</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36760</t>
+          <t>35681</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37564</t>
+          <t>38432</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64859</t>
+          <t>66009</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42612</t>
+          <t>42537</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71200</t>
+          <t>72563</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44658</t>
+          <t>44338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75012</t>
+          <t>73545</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94758</t>
+          <t>94009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135734</t>
+          <t>134671</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125777</t>
+          <t>125188</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>172777</t>
+          <t>169704</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100752</t>
+          <t>103295</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>144681</t>
+          <t>146100</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>238386</t>
+          <t>240080</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>302177</t>
+          <t>301789</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>625691</t>
+          <t>627015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>677948</t>
+          <t>681128</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>727737</t>
+          <t>726405</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>778236</t>
+          <t>777920</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1364955</t>
+          <t>1369843</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1442222</t>
+          <t>1442837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,45%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74304</t>
+          <t>76165</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>112180</t>
+          <t>112906</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53186</t>
+          <t>53099</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85756</t>
+          <t>87436</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>138520</t>
+          <t>135732</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>186316</t>
+          <t>187496</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>181575</t>
+          <t>183027</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>239539</t>
+          <t>239594</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>150292</t>
+          <t>150233</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>204387</t>
+          <t>203610</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>347011</t>
+          <t>345291</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>423478</t>
+          <t>423411</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>390074</t>
+          <t>388616</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>466033</t>
+          <t>467066</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>322920</t>
+          <t>323772</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>398306</t>
+          <t>397153</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>732318</t>
+          <t>733078</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>841281</t>
+          <t>842405</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2552588</t>
+          <t>2551806</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2650774</t>
+          <t>2650005</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2785315</t>
+          <t>2781651</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2878001</t>
+          <t>2872730</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5367477</t>
+          <t>5361204</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5503297</t>
+          <t>5498984</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2016</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2016 (tasa de respuesta: 97,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26833</t>
+          <t>28345</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>18889</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>16279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38032</t>
+          <t>39323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32267</t>
+          <t>32414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57887</t>
+          <t>57343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>14756</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34722</t>
+          <t>33366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49840</t>
+          <t>51008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83091</t>
+          <t>83499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105062</t>
+          <t>104617</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>144062</t>
+          <t>147442</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77712</t>
+          <t>78683</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>112764</t>
+          <t>114598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>194215</t>
+          <t>192015</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>247923</t>
+          <t>245773</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>442463</t>
+          <t>443353</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>489989</t>
+          <t>491150</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>506060</t>
+          <t>505389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>546158</t>
+          <t>544428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>961548</t>
+          <t>964560</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1024735</t>
+          <t>1026269</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,65%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>19698</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40566</t>
+          <t>40863</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19075</t>
+          <t>18381</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40369</t>
+          <t>39647</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42669</t>
+          <t>43696</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>73593</t>
+          <t>75681</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53080</t>
+          <t>53639</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87429</t>
+          <t>85698</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38608</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68566</t>
+          <t>65427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99303</t>
+          <t>97372</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142863</t>
+          <t>139492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166992</t>
+          <t>166497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>219949</t>
+          <t>218372</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153267</t>
+          <t>152333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>204708</t>
+          <t>202424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>333802</t>
+          <t>328615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>403838</t>
+          <t>403662</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>696317</t>
+          <t>691328</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>753368</t>
+          <t>751361</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>736624</t>
+          <t>740046</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>794456</t>
+          <t>799291</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1447960</t>
+          <t>1451515</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1531020</t>
+          <t>1534556</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,4%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46821</t>
+          <t>45915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78820</t>
+          <t>78787</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42560</t>
+          <t>43602</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72114</t>
+          <t>75060</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>98784</t>
+          <t>97540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141699</t>
+          <t>139862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91733</t>
+          <t>92995</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>134149</t>
+          <t>133121</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>98650</t>
+          <t>100014</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>138707</t>
+          <t>137566</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>202390</t>
+          <t>200944</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>256634</t>
+          <t>259574</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>124111</t>
+          <t>123833</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170852</t>
+          <t>166332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>122050</t>
+          <t>123913</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>166715</t>
+          <t>167190</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>260226</t>
+          <t>260626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>319285</t>
+          <t>320736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>400751</t>
+          <t>402117</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>457748</t>
+          <t>460145</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>417656</t>
+          <t>416383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>473103</t>
+          <t>471823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>833033</t>
+          <t>835432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>911337</t>
+          <t>912563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,38%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28466</t>
+          <t>29080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18480</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39405</t>
+          <t>40821</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35628</t>
+          <t>34838</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63227</t>
+          <t>62755</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47062</t>
+          <t>46868</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77103</t>
+          <t>76937</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46369</t>
+          <t>46774</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76724</t>
+          <t>76413</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100518</t>
+          <t>98800</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>143159</t>
+          <t>141774</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>117946</t>
+          <t>118809</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>160813</t>
+          <t>160473</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>121302</t>
+          <t>119411</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166611</t>
+          <t>166779</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>252717</t>
+          <t>251806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>314640</t>
+          <t>317341</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>665959</t>
+          <t>666470</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>716850</t>
+          <t>716744</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>749618</t>
+          <t>751297</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>805772</t>
+          <t>807114</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1434616</t>
+          <t>1433020</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1507872</t>
+          <t>1506002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>103248</t>
+          <t>103766</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>151080</t>
+          <t>151022</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>101424</t>
+          <t>100627</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>143639</t>
+          <t>144595</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>218709</t>
+          <t>217803</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>277734</t>
+          <t>280129</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>252536</t>
+          <t>252985</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>318875</t>
+          <t>321581</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>222822</t>
+          <t>222105</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>283877</t>
+          <t>283333</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>493361</t>
+          <t>493744</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>584579</t>
+          <t>582298</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>555280</t>
+          <t>553691</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>645461</t>
+          <t>643115</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>518184</t>
+          <t>515949</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>603986</t>
+          <t>602774</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1099669</t>
+          <t>1094586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1234586</t>
+          <t>1224712</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2253621</t>
+          <t>2256830</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2362549</t>
+          <t>2366174</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2466772</t>
+          <t>2463079</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2570087</t>
+          <t>2566664</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4754210</t>
+          <t>4750995</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4896070</t>
+          <t>4900282</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,35%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2023</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2023 (tasa de respuesta: 99,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13795</t>
+          <t>14532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29157</t>
+          <t>28877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61201</t>
+          <t>62574</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>33319</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49379</t>
+          <t>49805</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84577</t>
+          <t>87745</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48518</t>
+          <t>47278</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80495</t>
+          <t>84007</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44558</t>
+          <t>44376</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>66209</t>
+          <t>65372</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98552</t>
+          <t>100215</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>140876</t>
+          <t>139352</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>497331</t>
+          <t>499318</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>544132</t>
+          <t>543702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>576928</t>
+          <t>577532</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>604034</t>
+          <t>604321</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1085521</t>
+          <t>1085310</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1140136</t>
+          <t>1138527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>513</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21372</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24620</t>
+          <t>24073</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27577</t>
+          <t>29072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83892</t>
+          <t>85100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27743</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52416</t>
+          <t>51221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60820</t>
+          <t>62722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122748</t>
+          <t>122688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63182</t>
+          <t>59285</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158433</t>
+          <t>158698</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81158</t>
+          <t>80260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112884</t>
+          <t>113505</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144776</t>
+          <t>141756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>253442</t>
+          <t>253623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>946919</t>
+          <t>947034</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1083496</t>
+          <t>1101581</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>782696</t>
+          <t>781173</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>822680</t>
+          <t>822372</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1752329</t>
+          <t>1751930</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1914720</t>
+          <t>1911471</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>22031</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27667</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>38885</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73705</t>
+          <t>74786</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>14401</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44988</t>
+          <t>44264</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>55615</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>109847</t>
+          <t>108115</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>105458</t>
+          <t>103729</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157206</t>
+          <t>156263</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52688</t>
+          <t>54178</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148013</t>
+          <t>149612</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149975</t>
+          <t>152911</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>285654</t>
+          <t>285101</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>486868</t>
+          <t>485483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>543810</t>
+          <t>544199</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>728830</t>
+          <t>731514</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>858277</t>
+          <t>859727</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1233298</t>
+          <t>1235502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1415954</t>
+          <t>1420387</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,86%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>14473</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38478</t>
+          <t>36969</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>19408</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24182</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50604</t>
+          <t>51485</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57646</t>
+          <t>57704</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99160</t>
+          <t>96995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49877</t>
+          <t>49399</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81643</t>
+          <t>80083</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113553</t>
+          <t>114763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>167246</t>
+          <t>166474</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>97543</t>
+          <t>96691</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>151334</t>
+          <t>149949</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>84626</t>
+          <t>85525</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>129385</t>
+          <t>128796</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>195313</t>
+          <t>198462</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>264617</t>
+          <t>265779</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>673427</t>
+          <t>676501</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>737651</t>
+          <t>736885</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>879262</t>
+          <t>881046</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>942589</t>
+          <t>943305</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1571246</t>
+          <t>1570155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1662301</t>
+          <t>1659535</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24482</t>
+          <t>25100</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51632</t>
+          <t>51824</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,47 +12255,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>37880</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>25842</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>53253</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>37880</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>25811</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>52229</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>57884</t>
+          <t>55680</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>95498</t>
+          <t>93589</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>175362</t>
+          <t>180023</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>269993</t>
+          <t>269809</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>121540</t>
+          <t>126046</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>180156</t>
+          <t>184705</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>326182</t>
+          <t>322892</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>431376</t>
+          <t>436022</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>335544</t>
+          <t>326500</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>483080</t>
+          <t>482700</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>301876</t>
+          <t>302479</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>408291</t>
+          <t>410978</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>676752</t>
+          <t>682081</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>870707</t>
+          <t>876988</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2676350</t>
+          <t>2678778</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2909989</t>
+          <t>2914405</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3031195</t>
+          <t>3027825</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3193806</t>
+          <t>3184194</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5737597</t>
+          <t>5730527</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6024509</t>
+          <t>6022424</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P27_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P27_2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70528</t>
+          <t>68737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105606</t>
+          <t>104028</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34696</t>
+          <t>35315</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59741</t>
+          <t>60239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111871</t>
+          <t>112465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>155571</t>
+          <t>154121</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275438</t>
+          <t>274450</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>323594</t>
+          <t>325151</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231340</t>
+          <t>233246</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280799</t>
+          <t>280331</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>522976</t>
+          <t>518145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>587603</t>
+          <t>588255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,19%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>134400</t>
+          <t>132804</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>177713</t>
+          <t>175649</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>148456</t>
+          <t>146816</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>193226</t>
+          <t>194023</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>297044</t>
+          <t>295375</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>358923</t>
+          <t>353512</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102560</t>
+          <t>101761</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>140787</t>
+          <t>142603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147132</t>
+          <t>147754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>190414</t>
+          <t>190982</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>259679</t>
+          <t>260363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>317719</t>
+          <t>322730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>116044</t>
+          <t>117110</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>163024</t>
+          <t>162412</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64565</t>
+          <t>64406</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>98610</t>
+          <t>99680</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>192567</t>
+          <t>193673</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>248056</t>
+          <t>247891</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>344092</t>
+          <t>344425</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>405228</t>
+          <t>405695</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>278814</t>
+          <t>275972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>336922</t>
+          <t>335918</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>638280</t>
+          <t>638579</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>722331</t>
+          <t>727356</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>209842</t>
+          <t>210160</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>265925</t>
+          <t>263945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>252493</t>
+          <t>253341</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307640</t>
+          <t>309611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>473259</t>
+          <t>476107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>555253</t>
+          <t>554033</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>149577</t>
+          <t>149984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>198177</t>
+          <t>199361</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>241198</t>
+          <t>241677</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>297050</t>
+          <t>296195</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>404362</t>
+          <t>401463</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>478835</t>
+          <t>480596</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>51218</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82784</t>
+          <t>81367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>34612</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60501</t>
+          <t>60290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92547</t>
+          <t>93854</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>134622</t>
+          <t>133759</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>238782</t>
+          <t>237159</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>292869</t>
+          <t>289011</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>161493</t>
+          <t>159613</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>207591</t>
+          <t>204165</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>410923</t>
+          <t>410917</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>480706</t>
+          <t>482905</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139764</t>
+          <t>137059</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>183153</t>
+          <t>182885</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>159844</t>
+          <t>155733</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204187</t>
+          <t>202244</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>309089</t>
+          <t>309197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>374937</t>
+          <t>379561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139426</t>
+          <t>139415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>182922</t>
+          <t>184042</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>228382</t>
+          <t>226931</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>276868</t>
+          <t>274408</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>379407</t>
+          <t>379175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>446301</t>
+          <t>448269</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118088</t>
+          <t>120784</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>160107</t>
+          <t>161972</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73143</t>
+          <t>73345</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>110855</t>
+          <t>110356</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>203836</t>
+          <t>206109</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>260589</t>
+          <t>259903</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>311481</t>
+          <t>310101</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>366903</t>
+          <t>365539</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>305849</t>
+          <t>306235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>366767</t>
+          <t>366980</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>631891</t>
+          <t>629508</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>713459</t>
+          <t>713975</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>220344</t>
+          <t>220430</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>273210</t>
+          <t>271818</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>245686</t>
+          <t>246788</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>303122</t>
+          <t>303262</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>481152</t>
+          <t>481890</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>557908</t>
+          <t>553470</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138266</t>
+          <t>136250</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>179355</t>
+          <t>180805</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>244853</t>
+          <t>242581</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>301721</t>
+          <t>300326</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>390910</t>
+          <t>396318</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>460771</t>
+          <t>473849</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>391302</t>
+          <t>393786</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>469969</t>
+          <t>471211</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>236178</t>
+          <t>234578</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>297364</t>
+          <t>295878</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>645550</t>
+          <t>641636</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>747682</t>
+          <t>744661</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1220083</t>
+          <t>1227795</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1329544</t>
+          <t>1334265</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1024648</t>
+          <t>1028513</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1133255</t>
+          <t>1131020</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2275752</t>
+          <t>2281359</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2434026</t>
+          <t>2440692</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>749669</t>
+          <t>745061</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>846049</t>
+          <t>847197</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>853016</t>
+          <t>854726</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>951071</t>
+          <t>951844</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1635900</t>
+          <t>1624444</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1783378</t>
+          <t>1770962</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>570250</t>
+          <t>570737</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>662103</t>
+          <t>660272</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>910868</t>
+          <t>907407</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1010245</t>
+          <t>1018057</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1506877</t>
+          <t>1501433</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1640378</t>
+          <t>1643285</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27752</t>
+          <t>28555</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20035</t>
+          <t>20212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>21053</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41192</t>
+          <t>41854</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40618</t>
+          <t>40112</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68787</t>
+          <t>68305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>20092</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43602</t>
+          <t>41302</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66815</t>
+          <t>66952</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101700</t>
+          <t>103818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67672</t>
+          <t>69028</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102114</t>
+          <t>103147</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59348</t>
+          <t>59581</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93086</t>
+          <t>95119</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>136364</t>
+          <t>137922</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>185414</t>
+          <t>185284</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>522367</t>
+          <t>523328</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>565511</t>
+          <t>565810</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>548457</t>
+          <t>549092</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>589600</t>
+          <t>590572</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1080605</t>
+          <t>1084496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1144252</t>
+          <t>1146250</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,7%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>23794</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47448</t>
+          <t>46711</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>15667</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36857</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>44904</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>75034</t>
+          <t>75058</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57060</t>
+          <t>55984</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92044</t>
+          <t>89598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>42513</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72547</t>
+          <t>71344</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105910</t>
+          <t>106672</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153184</t>
+          <t>153085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99547</t>
+          <t>100201</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140765</t>
+          <t>144073</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75149</t>
+          <t>73485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112563</t>
+          <t>111295</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182756</t>
+          <t>180951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>238728</t>
+          <t>240213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>754136</t>
+          <t>753494</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>806820</t>
+          <t>808182</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>823999</t>
+          <t>824901</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>872047</t>
+          <t>873852</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1593116</t>
+          <t>1591745</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1668057</t>
+          <t>1668053</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24305</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33796</t>
+          <t>34031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>18767</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40248</t>
+          <t>40597</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23672</t>
+          <t>22715</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46738</t>
+          <t>46508</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>46576</t>
+          <t>47088</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>78478</t>
+          <t>79303</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63347</t>
+          <t>62128</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98481</t>
+          <t>98264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56256</t>
+          <t>54854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89560</t>
+          <t>89280</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124516</t>
+          <t>125155</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172495</t>
+          <t>173432</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>598549</t>
+          <t>598237</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>641238</t>
+          <t>640791</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>636099</t>
+          <t>636413</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>674669</t>
+          <t>676724</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1250345</t>
+          <t>1245167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1307999</t>
+          <t>1305567</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17208</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37308</t>
+          <t>36187</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>16349</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35681</t>
+          <t>34843</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38432</t>
+          <t>37367</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66009</t>
+          <t>64737</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42537</t>
+          <t>43810</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72563</t>
+          <t>71722</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44338</t>
+          <t>43656</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73545</t>
+          <t>73278</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94009</t>
+          <t>95527</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134671</t>
+          <t>137507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125188</t>
+          <t>123384</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>169704</t>
+          <t>170484</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>103295</t>
+          <t>101967</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>146100</t>
+          <t>143007</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>240080</t>
+          <t>237812</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>301789</t>
+          <t>300372</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>627015</t>
+          <t>626016</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>681128</t>
+          <t>680394</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>726405</t>
+          <t>727551</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>777920</t>
+          <t>778180</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1369843</t>
+          <t>1367583</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1442837</t>
+          <t>1443053</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>76165</t>
+          <t>73964</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>112906</t>
+          <t>112699</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53099</t>
+          <t>52844</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>87436</t>
+          <t>85894</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>135732</t>
+          <t>137101</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>187496</t>
+          <t>187158</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>183027</t>
+          <t>180890</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>239594</t>
+          <t>237390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>150233</t>
+          <t>151947</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203610</t>
+          <t>203972</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>345291</t>
+          <t>345851</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>423411</t>
+          <t>425169</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>388616</t>
+          <t>391595</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>467066</t>
+          <t>465937</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>323772</t>
+          <t>323999</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>397153</t>
+          <t>398055</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>733078</t>
+          <t>735773</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>842405</t>
+          <t>838687</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2551806</t>
+          <t>2557919</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2650005</t>
+          <t>2647283</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2781651</t>
+          <t>2778936</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2872730</t>
+          <t>2873352</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5361204</t>
+          <t>5363051</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5498984</t>
+          <t>5495696</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9652</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>27573</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18889</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>16935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39323</t>
+          <t>38348</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32414</t>
+          <t>32557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57343</t>
+          <t>58660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33366</t>
+          <t>32843</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51008</t>
+          <t>50737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83499</t>
+          <t>82760</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104617</t>
+          <t>102703</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>147442</t>
+          <t>144938</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78683</t>
+          <t>78427</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>114598</t>
+          <t>115675</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>192015</t>
+          <t>193640</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>245773</t>
+          <t>247144</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>443353</t>
+          <t>444155</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>491150</t>
+          <t>491673</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>505389</t>
+          <t>505753</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>544428</t>
+          <t>545160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>964560</t>
+          <t>964221</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1026269</t>
+          <t>1023089</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19698</t>
+          <t>18557</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18381</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39647</t>
+          <t>40437</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43696</t>
+          <t>43155</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>75681</t>
+          <t>72079</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53639</t>
+          <t>53505</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85698</t>
+          <t>89635</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38608</t>
+          <t>38152</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65427</t>
+          <t>65498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97372</t>
+          <t>98366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139492</t>
+          <t>143329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166497</t>
+          <t>165927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218372</t>
+          <t>217963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152333</t>
+          <t>153734</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202424</t>
+          <t>201804</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328615</t>
+          <t>332111</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>403662</t>
+          <t>401346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>691328</t>
+          <t>692858</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>751361</t>
+          <t>753591</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>740046</t>
+          <t>737263</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>799291</t>
+          <t>792063</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1451515</t>
+          <t>1447012</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1534556</t>
+          <t>1531307</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,24%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45915</t>
+          <t>46830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78787</t>
+          <t>77129</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43602</t>
+          <t>42625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75060</t>
+          <t>73640</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97540</t>
+          <t>99417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139862</t>
+          <t>142820</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92995</t>
+          <t>92336</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>133121</t>
+          <t>132197</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100014</t>
+          <t>99513</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>137566</t>
+          <t>139308</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>200944</t>
+          <t>201409</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>259574</t>
+          <t>255455</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123833</t>
+          <t>125923</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>166332</t>
+          <t>171102</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123913</t>
+          <t>121562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>167190</t>
+          <t>166008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>260626</t>
+          <t>262455</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320736</t>
+          <t>323855</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>402117</t>
+          <t>401324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>460145</t>
+          <t>456566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>416383</t>
+          <t>417789</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>471823</t>
+          <t>472393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>835432</t>
+          <t>832720</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>912563</t>
+          <t>909587</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11364</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>29675</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18897</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40821</t>
+          <t>39742</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34838</t>
+          <t>34866</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62755</t>
+          <t>61720</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46868</t>
+          <t>48298</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>76937</t>
+          <t>77410</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46774</t>
+          <t>45778</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76413</t>
+          <t>77473</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98800</t>
+          <t>103272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>141774</t>
+          <t>146277</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>118809</t>
+          <t>119561</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>160473</t>
+          <t>162322</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>119411</t>
+          <t>119975</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166779</t>
+          <t>165274</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,47 +8870,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
+          <t>16,35%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>281345</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>251081</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>317127</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>14,64%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>13,07%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>16,5%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>281345</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>251806</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>317341</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>666470</t>
+          <t>663831</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>716744</t>
+          <t>718055</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>751297</t>
+          <t>753758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>807114</t>
+          <t>807419</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1433020</t>
+          <t>1428864</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1506002</t>
+          <t>1507977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,47%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>103766</t>
+          <t>103116</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>151022</t>
+          <t>149279</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100627</t>
+          <t>102367</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>144595</t>
+          <t>147349</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>217803</t>
+          <t>217372</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>280129</t>
+          <t>281571</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>252985</t>
+          <t>249965</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>321581</t>
+          <t>319485</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>222105</t>
+          <t>220676</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>283333</t>
+          <t>283091</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>493744</t>
+          <t>493931</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>582298</t>
+          <t>581495</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>553691</t>
+          <t>556333</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>643115</t>
+          <t>645070</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>515949</t>
+          <t>517920</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>602774</t>
+          <t>604365</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1094586</t>
+          <t>1091237</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1224712</t>
+          <t>1218496</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2256830</t>
+          <t>2259809</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2366174</t>
+          <t>2366394</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2463079</t>
+          <t>2464139</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2566664</t>
+          <t>2569572</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4750995</t>
+          <t>4756782</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4900282</t>
+          <t>4911263</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,51%</t>
         </is>
       </c>
     </row>
@@ -9959,69 +9959,69 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6495</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1767</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6164</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>12</t>
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>9741</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14532</t>
+          <t>17790</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41191</t>
+          <t>40694</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28877</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62574</t>
+          <t>57831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24153</t>
+          <t>24902</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17048</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33319</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>65344</t>
+          <t>65597</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49805</t>
+          <t>51388</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87745</t>
+          <t>84329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62261</t>
+          <t>69365</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47278</t>
+          <t>53858</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84007</t>
+          <t>88223</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54483</t>
+          <t>55717</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44376</t>
+          <t>45831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65372</t>
+          <t>66993</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116744</t>
+          <t>125082</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>100215</t>
+          <t>107592</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>139352</t>
+          <t>147177</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>523621</t>
+          <t>570052</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>499318</t>
+          <t>547562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>543702</t>
+          <t>588403</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>591606</t>
+          <t>646037</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>577532</t>
+          <t>630616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>604321</t>
+          <t>658571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1115227</t>
+          <t>1216089</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1085310</t>
+          <t>1189537</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1138527</t>
+          <t>1243128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,76%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>632726</t>
+          <t>687442</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>632726</t>
+          <t>687442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>632726</t>
+          <t>687442</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>672010</t>
+          <t>729067</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>672010</t>
+          <t>729067</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>672010</t>
+          <t>729067</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1304736</t>
+          <t>1416509</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1304736</t>
+          <t>1416509</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1304736</t>
+          <t>1416509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,27 +10528,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>14639</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>24347</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>16891</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24073</t>
+          <t>26784</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>55707</t>
+          <t>54761</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29072</t>
+          <t>40115</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85100</t>
+          <t>76244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37887</t>
+          <t>39729</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>28999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51221</t>
+          <t>55389</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>93595</t>
+          <t>94490</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62722</t>
+          <t>76116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122688</t>
+          <t>119008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>114434</t>
+          <t>123448</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59285</t>
+          <t>99237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158698</t>
+          <t>150323</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95893</t>
+          <t>112319</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80260</t>
+          <t>95381</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113505</t>
+          <t>130738</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>210326</t>
+          <t>235767</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141756</t>
+          <t>205215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>253623</t>
+          <t>269429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1007526</t>
+          <t>863012</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>947034</t>
+          <t>831228</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1101581</t>
+          <t>891244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>803498</t>
+          <t>894460</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>781173</t>
+          <t>871495</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>822372</t>
+          <t>915434</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1811025</t>
+          <t>1757473</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1751930</t>
+          <t>1720126</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1911471</t>
+          <t>1793935</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>85,24%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1179939</t>
+          <t>1043474</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1179939</t>
+          <t>1043474</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1179939</t>
+          <t>1043474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>950473</t>
+          <t>1061147</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>950473</t>
+          <t>1061147</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>950473</t>
+          <t>1061147</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2130413</t>
+          <t>2104621</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2130413</t>
+          <t>2104621</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2130413</t>
+          <t>2104621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11699</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22031</t>
+          <t>25077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15990</t>
+          <t>18997</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>10837</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53722</t>
+          <t>55426</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38885</t>
+          <t>39551</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74786</t>
+          <t>76620</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29746</t>
+          <t>31836</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>23156</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44264</t>
+          <t>43073</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>83468</t>
+          <t>87262</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>70017</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>108115</t>
+          <t>109573</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -11323,22 +11323,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>129102</t>
+          <t>140911</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103729</t>
+          <t>118079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>156263</t>
+          <t>169335</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>107821</t>
+          <t>116879</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54178</t>
+          <t>100206</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149612</t>
+          <t>137691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>236922</t>
+          <t>257790</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152911</t>
+          <t>226532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>285101</t>
+          <t>291644</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>515557</t>
+          <t>599265</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>485483</t>
+          <t>566833</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>544199</t>
+          <t>626340</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>783395</t>
+          <t>644580</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>731514</t>
+          <t>621689</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>859727</t>
+          <t>666414</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1298952</t>
+          <t>1243844</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1235502</t>
+          <t>1207697</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1420387</t>
+          <t>1279660</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>79,59%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>703230</t>
+          <t>800526</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>703230</t>
+          <t>800526</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>703230</t>
+          <t>800526</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>932102</t>
+          <t>807367</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>932102</t>
+          <t>807367</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>932102</t>
+          <t>807367</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1635332</t>
+          <t>1607893</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1635332</t>
+          <t>1607893</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1635332</t>
+          <t>1607893</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23783</t>
+          <t>29533</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14473</t>
+          <t>18313</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36969</t>
+          <t>46930</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11778</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19408</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24599</t>
+          <t>30547</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51485</t>
+          <t>60072</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>75593</t>
+          <t>78949</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57704</t>
+          <t>60828</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96995</t>
+          <t>103616</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>64004</t>
+          <t>67175</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49399</t>
+          <t>53305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80083</t>
+          <t>83571</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>139598</t>
+          <t>146124</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>114763</t>
+          <t>124799</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>166474</t>
+          <t>175369</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>119831</t>
+          <t>114533</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>96691</t>
+          <t>90883</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>149949</t>
+          <t>137142</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>109446</t>
+          <t>111134</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>85525</t>
+          <t>94171</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>128796</t>
+          <t>130147</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>229277</t>
+          <t>225668</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>198462</t>
+          <t>200141</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>265779</t>
+          <t>253036</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>707459</t>
+          <t>765929</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>676501</t>
+          <t>737781</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>736885</t>
+          <t>795526</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>906065</t>
+          <t>923647</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>881046</t>
+          <t>899561</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>943305</t>
+          <t>945870</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1613524</t>
+          <t>1689577</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1570155</t>
+          <t>1655628</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1659535</t>
+          <t>1727434</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,06%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1091293</t>
+          <t>1116079</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1091293</t>
+          <t>1116079</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1091293</t>
+          <t>1116079</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2017960</t>
+          <t>2105024</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2017960</t>
+          <t>2105024</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2017960</t>
+          <t>2105024</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>36559</t>
+          <t>44041</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25100</t>
+          <t>29986</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51824</t>
+          <t>62527</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37880</t>
+          <t>45244</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25842</t>
+          <t>33797</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53253</t>
+          <t>61531</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>74439</t>
+          <t>89284</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>55680</t>
+          <t>70709</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>93589</t>
+          <t>113015</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>226213</t>
+          <t>229830</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>180023</t>
+          <t>196040</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>269809</t>
+          <t>265874</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>155791</t>
+          <t>163642</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126046</t>
+          <t>139935</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>184705</t>
+          <t>186596</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>382004</t>
+          <t>393473</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>322892</t>
+          <t>354153</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>436022</t>
+          <t>435121</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>425628</t>
+          <t>448257</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>326500</t>
+          <t>408660</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>482700</t>
+          <t>498848</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>367642</t>
+          <t>396049</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>302479</t>
+          <t>363217</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>410978</t>
+          <t>427601</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>793270</t>
+          <t>844306</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>682081</t>
+          <t>782432</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>876988</t>
+          <t>898237</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2754162</t>
+          <t>2798258</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2678778</t>
+          <t>2745209</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2914405</t>
+          <t>2848663</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3084566</t>
+          <t>3108726</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3027825</t>
+          <t>3063883</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3184194</t>
+          <t>3146676</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>5838727</t>
+          <t>5906984</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5730527</t>
+          <t>5838479</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6022424</t>
+          <t>5973707</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3442562</t>
+          <t>3520386</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3442562</t>
+          <t>3520386</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3442562</t>
+          <t>3520386</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3645879</t>
+          <t>3713661</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3645879</t>
+          <t>3713661</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3645879</t>
+          <t>3713661</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7088440</t>
+          <t>7234047</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7088440</t>
+          <t>7234047</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7088440</t>
+          <t>7234047</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
